--- a/trade-elasticities-cointegration/outputs/section_12_model_diagnostics.xlsx
+++ b/trade-elasticities-cointegration/outputs/section_12_model_diagnostics.xlsx
@@ -527,7 +527,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -695,33 +695,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D3">
-        <v>0.8881066849164436</v>
+        <v>0.1105463733663874</v>
       </c>
       <c r="E3">
-        <v>0.210634350170605</v>
+        <v>0.535991066053781</v>
       </c>
       <c r="F3">
-        <v>0.6622367556746986</v>
+        <v>0.1724643085827477</v>
       </c>
       <c r="G3">
-        <v>0.9560040278563603</v>
+        <v>0.2577772109866205</v>
       </c>
       <c r="H3">
-        <v>0.789427366893068</v>
+        <v>0.9454589346969281</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -780,23 +780,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D4">
-        <v>0.1105463733663874</v>
+        <v>0.1414347456519745</v>
       </c>
       <c r="E4">
-        <v>0.535991066053781</v>
+        <v>0.846998319281811</v>
       </c>
       <c r="F4">
-        <v>0.1724643085827477</v>
+        <v>0.411018318616428</v>
       </c>
       <c r="G4">
-        <v>0.2577772109866205</v>
+        <v>0.2812534709451062</v>
       </c>
       <c r="H4">
-        <v>0.9454589346969281</v>
+        <v>0.4901623900409602</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -837,81 +837,6 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>mantener especificacion e interpretar coeficientes HAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.1414347456519745</v>
-      </c>
-      <c r="E5">
-        <v>0.846998319281811</v>
-      </c>
-      <c r="F5">
-        <v>0.411018318616428</v>
-      </c>
-      <c r="G5">
-        <v>0.2812534709451062</v>
-      </c>
-      <c r="H5">
-        <v>0.4901623900409602</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>p-valores altos no rechazan el supuesto diagnostico correspondiente</t>
-        </is>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>sin alertas diagnosticas al 5%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>apto para tabla principal</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
         <is>
           <t>mantener especificacion e interpretar coeficientes HAC</t>
         </is>
@@ -924,7 +849,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1107,17 +1032,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1142,17 +1067,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1177,17 +1102,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1212,17 +1137,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1247,7 +1172,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1257,7 +1182,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1282,7 +1207,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1292,7 +1217,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1317,7 +1242,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1327,7 +1252,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1352,7 +1277,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1362,7 +1287,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1381,146 +1306,6 @@
         </is>
       </c>
       <c r="G13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>autocorrelation_flag</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>autocorrelacion</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>instability_flag</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>estabilidad</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>heteroskedasticity_flag</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>heterocedasticidad</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>non_normality_flag</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>normalidad</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1531,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1797,33 +1582,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D3">
-        <v>0.8881066849164436</v>
+        <v>0.1105463733663874</v>
       </c>
       <c r="E3">
-        <v>0.210634350170605</v>
+        <v>0.535991066053781</v>
       </c>
       <c r="F3">
-        <v>0.6622367556746986</v>
+        <v>0.1724643085827477</v>
       </c>
       <c r="G3">
-        <v>0.9560040278563603</v>
+        <v>0.2577772109866205</v>
       </c>
       <c r="H3">
-        <v>0.789427366893068</v>
+        <v>0.9454589346969281</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1872,23 +1657,23 @@
         <v>71</v>
       </c>
       <c r="S3">
-        <v>0.6775189342091898</v>
+        <v>0.7489780092599264</v>
       </c>
       <c r="T3">
-        <v>0.6237720899107215</v>
+        <v>0.7254446976280445</v>
       </c>
       <c r="U3">
-        <v>-161.883561029474</v>
+        <v>-231.4270217230853</v>
       </c>
       <c r="V3">
-        <v>-134.7314025049782</v>
+        <v>-213.3255827067548</v>
       </c>
       <c r="W3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>modelo ECM con termino de correccion del error rezagado</t>
+          <t>modelo de corto plazo en primeras diferencias</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1896,32 +1681,16 @@
           <t>BIC</t>
         </is>
       </c>
-      <c r="Z3">
-        <v>-0.3296877998473486</v>
-      </c>
-      <c r="AA3">
-        <v>0.01546877443348586</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>estable: convergencia gradual</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>corrige aproximadamente 33% del desequilibrio por trimestre</t>
-        </is>
-      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>ECM con ajuste significativo y sin alertas diagnosticas al 5%</t>
+          <t>modelo en diferencias sin alertas diagnosticas al 5%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1931,23 +1700,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D4">
-        <v>0.1105463733663874</v>
+        <v>0.1414347456519745</v>
       </c>
       <c r="E4">
-        <v>0.535991066053781</v>
+        <v>0.846998319281811</v>
       </c>
       <c r="F4">
-        <v>0.1724643085827477</v>
+        <v>0.411018318616428</v>
       </c>
       <c r="G4">
-        <v>0.2577772109866205</v>
+        <v>0.2812534709451062</v>
       </c>
       <c r="H4">
-        <v>0.9454589346969281</v>
+        <v>0.4901623900409602</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1996,23 +1765,23 @@
         <v>71</v>
       </c>
       <c r="S4">
-        <v>0.7489780092599264</v>
+        <v>0.7978164645129172</v>
       </c>
       <c r="T4">
-        <v>0.7254446976280445</v>
+        <v>0.7679861068181018</v>
       </c>
       <c r="U4">
-        <v>-231.4270217230853</v>
+        <v>-240.7889133926478</v>
       </c>
       <c r="V4">
-        <v>-213.3255827067548</v>
+        <v>-215.8994347451933</v>
       </c>
       <c r="W4">
         <v>4</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>modelo de corto plazo en primeras diferencias</t>
+          <t>modelo ECM con termino de correccion del error rezagado</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -2020,131 +1789,23 @@
           <t>BIC</t>
         </is>
       </c>
+      <c r="Z4">
+        <v>-0.3289306816518565</v>
+      </c>
+      <c r="AA4">
+        <v>3.707512354853029E-08</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>estable: convergencia gradual</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>corrige aproximadamente 32.9% del desequilibrio por trimestre</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr">
-        <is>
-          <t>modelo en diferencias sin alertas diagnosticas al 5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.1414347456519745</v>
-      </c>
-      <c r="E5">
-        <v>0.846998319281811</v>
-      </c>
-      <c r="F5">
-        <v>0.411018318616428</v>
-      </c>
-      <c r="G5">
-        <v>0.2812534709451062</v>
-      </c>
-      <c r="H5">
-        <v>0.4901623900409602</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>p-valores altos no rechazan el supuesto diagnostico correspondiente</t>
-        </is>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>sin alertas diagnosticas al 5%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>apto para tabla principal</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>mantener especificacion e interpretar coeficientes HAC</t>
-        </is>
-      </c>
-      <c r="R5">
-        <v>71</v>
-      </c>
-      <c r="S5">
-        <v>0.7978164645129172</v>
-      </c>
-      <c r="T5">
-        <v>0.7679861068181018</v>
-      </c>
-      <c r="U5">
-        <v>-240.7889133926478</v>
-      </c>
-      <c r="V5">
-        <v>-215.8994347451933</v>
-      </c>
-      <c r="W5">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>modelo ECM con termino de correccion del error rezagado</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="Z5">
-        <v>-0.3289306816518565</v>
-      </c>
-      <c r="AA5">
-        <v>3.707512354853029E-08</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>estable: convergencia gradual</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>corrige aproximadamente 32.9% del desequilibrio por trimestre</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
         <is>
           <t>ECM con ajuste significativo y sin alertas diagnosticas al 5%</t>
         </is>
